--- a/tame_output/ON/bt/strategyON_20240803.xlsx
+++ b/tame_output/ON/bt/strategyON_20240803.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.0%</t>
+          <t>-680.8%</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.7%</t>
+          <t>-200.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.0%</t>
+          <t>-226.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.7%</t>
+          <t>-64.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2043"/>
+  <dimension ref="A1:G2044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.783240727848819</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48550,6 +48550,29 @@
       </c>
       <c r="G2043" t="n">
         <v>3.813238979600393</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="2" t="n">
+        <v>45506</v>
+      </c>
+      <c r="B2044" t="n">
+        <v>3.741353902931093</v>
+      </c>
+      <c r="C2044" t="n">
+        <v>3.831246438464132</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>-5.192212033979113</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>1.754005200558739</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>-0.02848069135753978</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>3.814158023649608</v>
       </c>
     </row>
   </sheetData>
